--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -619,7 +619,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-05-30 22:16 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-05-31 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -152,6 +152,8 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -594,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -619,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-05-31 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -639,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -655,7 +657,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -671,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>305.61</v>
+        <v>303.85</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -686,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>127.8</v>
+        <v>128.565</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -701,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.391</v>
+        <v>1.363</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -725,71 +727,86 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>comps_percentile</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>dcf_margin</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Normalized (intrinsic − market) / market, clipped ±50%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Honest caveats (read before acting)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
-        </is>
-      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -799,6 +816,7 @@
   <mergeCells count="11">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
@@ -807,7 +825,6 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -874,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0445300006866455</v>
+        <v>0.0447700023651123</v>
       </c>
     </row>
     <row r="6">
@@ -1203,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125785467.7934272</v>
+        <v>125785463.1042663</v>
       </c>
     </row>
     <row r="36">
@@ -1224,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>127.8</v>
+        <v>128.565</v>
       </c>
     </row>
     <row r="38">
@@ -1429,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1503,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>16075382784</v>
+        <v>16171608064</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.69</v>
+        <v>11.76</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>9.41</v>
@@ -1515,56 +1532,254 @@
         <v>1.3</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Broadridge Financial Solutions,</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>18424367104</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>17.037434</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>11.851</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>2.852</v>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>17564821504</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>16.767075</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>10.894</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FLEX</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Flex Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>54401626112</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>64.00216</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>27.824</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>2.053</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GIB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CGI Inc.</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>14911755264</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>12.87613</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>6.267</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>1.121</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HPQ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HP Inc.</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>26886967296</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>10.888888</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>6.768</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>0.555</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gartner, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>11961958400</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>17.654644</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>9.385</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>1.938</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NTAP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NetApp, Inc.</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>34599161856</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>27.553627</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TDY</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Teledyne Technologies Incorpora</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>28401612800</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>31.102993</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>19.938</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>4.927</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D7" s="33">
-        <f>MEDIAN(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E7" s="33">
-        <f>MEDIAN(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F7" s="33">
-        <f>MEDIAN(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="D15" s="35">
+        <f>MEDIAN(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E15" s="35">
+        <f>MEDIAN(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="35">
+        <f>MEDIAN(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D8" s="33">
-        <f>AVERAGE(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E8" s="33">
-        <f>AVERAGE(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F8" s="33">
-        <f>AVERAGE(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="D16" s="35">
+        <f>AVERAGE(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E16" s="35">
+        <f>AVERAGE(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F16" s="35">
+        <f>AVERAGE(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="34" t="n"/>
-      <c r="F9" s="34" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D17" s="36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="E17" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-02 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.806</v>
+        <v>0.83</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>303.85</v>
+        <v>305.31</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>128.565</v>
+        <v>126.46</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.363</v>
+        <v>1.414</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.611</v>
+        <v>0.667</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0447700023651123</v>
+        <v>0.04456999778747558</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125785463.1042663</v>
+        <v>125785460.3194686</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>128.565</v>
+        <v>126.46</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>16171608064</v>
+        <v>15906829312</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.76</v>
+        <v>11.57</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>1.3</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>18424367104</v>
+        <v>17806751744</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>17.037434</v>
+        <v>16.448719</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>11.851</v>
+        <v>12.261</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.852</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>17564821504</v>
+        <v>17770506240</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>16.767075</v>
+        <v>16.942753</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>10.894</v>
+        <v>11.895</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.9429999999999999</v>
+        <v>1.029</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>54401626112</v>
+        <v>57198919680</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>64.00216</v>
+        <v>67.29310599999999</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>27.824</v>
+        <v>27.332</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.053</v>
+        <v>2.017</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>14911755264</v>
+        <v>14420664320</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>12.87613</v>
+        <v>12.407207</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>6.267</v>
+        <v>6.366</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.121</v>
+        <v>1.139</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>26886967296</v>
+        <v>25382576128</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>10.888888</v>
+        <v>10.279629</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>6.768</v>
+        <v>7.214</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.555</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>11961958400</v>
+        <v>11460154368</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>17.654644</v>
+        <v>16.897335</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>9.385</v>
+        <v>10.256</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>1.938</v>
+        <v>2.118</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>34599161856</v>
+        <v>34769494016</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>27.553627</v>
+        <v>27.689274</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>17.54</v>
+        <v>18.102</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.8</v>
+        <v>4.954</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>28401612800</v>
+        <v>28335362048</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>31.102993</v>
+        <v>30.967594</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.938</v>
+        <v>19.626</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>4.927</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="15">
@@ -1772,7 +1772,7 @@
         <v>0.167</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="F17" s="36" t="n">
         <v>0.5</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -152,8 +152,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -596,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -621,7 +619,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-02 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-06 04:16 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +639,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -657,7 +655,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -673,7 +671,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>305.31</v>
+        <v>299.61</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +686,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>126.46</v>
+        <v>124.43</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +701,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.414</v>
+        <v>1.408</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,86 +725,71 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>comps_percentile</t>
+          <t>dcf_margin</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>dcf_margin</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
           <t>Normalized (intrinsic − market) / market, clipped ±50%</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Honest caveats (read before acting)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Honest caveats (read before acting)</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -816,7 +799,6 @@
   <mergeCells count="11">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
@@ -825,6 +807,7 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -891,7 +874,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04456999778747558</v>
+        <v>0.0453600025177002</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1203,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125785460.3194686</v>
+        <v>125785467.2988829</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1224,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>126.46</v>
+        <v>124.43</v>
       </c>
     </row>
     <row r="38">
@@ -1446,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1520,266 +1503,68 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>15906829312</v>
+        <v>15651485696</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.57</v>
+        <v>11.39</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.4</v>
+        <v>9.23</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Broadridge Financial Solutions,</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="n">
-        <v>17806751744</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <v>16.448719</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <v>12.261</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>2.95</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CDW</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CDW Corporation</t>
-        </is>
-      </c>
-      <c r="C7" s="33" t="n">
-        <v>17770506240</v>
-      </c>
-      <c r="D7" s="34" t="n">
-        <v>16.942753</v>
-      </c>
-      <c r="E7" s="34" t="n">
-        <v>11.895</v>
-      </c>
-      <c r="F7" s="34" t="n">
-        <v>1.029</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Peer median</t>
+        </is>
+      </c>
+      <c r="D7" s="33">
+        <f>MEDIAN(D6:D5)</f>
+        <v/>
+      </c>
+      <c r="E7" s="33">
+        <f>MEDIAN(E6:E5)</f>
+        <v/>
+      </c>
+      <c r="F7" s="33">
+        <f>MEDIAN(F6:F5)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FLEX</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Flex Ltd.</t>
-        </is>
-      </c>
-      <c r="C8" s="33" t="n">
-        <v>57198919680</v>
-      </c>
-      <c r="D8" s="34" t="n">
-        <v>67.29310599999999</v>
-      </c>
-      <c r="E8" s="34" t="n">
-        <v>27.332</v>
-      </c>
-      <c r="F8" s="34" t="n">
-        <v>2.017</v>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Peer mean</t>
+        </is>
+      </c>
+      <c r="D8" s="33">
+        <f>AVERAGE(D6:D5)</f>
+        <v/>
+      </c>
+      <c r="E8" s="33">
+        <f>AVERAGE(E6:E5)</f>
+        <v/>
+      </c>
+      <c r="F8" s="33">
+        <f>AVERAGE(F6:F5)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GIB</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CGI Inc.</t>
-        </is>
-      </c>
-      <c r="C9" s="33" t="n">
-        <v>14420664320</v>
-      </c>
-      <c r="D9" s="34" t="n">
-        <v>12.407207</v>
-      </c>
-      <c r="E9" s="34" t="n">
-        <v>6.366</v>
-      </c>
-      <c r="F9" s="34" t="n">
-        <v>1.139</v>
-      </c>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Target percentile vs peers</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>HPQ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HP Inc.</t>
-        </is>
-      </c>
-      <c r="C10" s="33" t="n">
-        <v>25382576128</v>
-      </c>
-      <c r="D10" s="34" t="n">
-        <v>10.279629</v>
-      </c>
-      <c r="E10" s="34" t="n">
-        <v>7.214</v>
-      </c>
-      <c r="F10" s="34" t="n">
-        <v>0.592</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Gartner, Inc.</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="n">
-        <v>11460154368</v>
-      </c>
-      <c r="D11" s="34" t="n">
-        <v>16.897335</v>
-      </c>
-      <c r="E11" s="34" t="n">
-        <v>10.256</v>
-      </c>
-      <c r="F11" s="34" t="n">
-        <v>2.118</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NTAP</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NetApp, Inc.</t>
-        </is>
-      </c>
-      <c r="C12" s="33" t="n">
-        <v>34769494016</v>
-      </c>
-      <c r="D12" s="34" t="n">
-        <v>27.689274</v>
-      </c>
-      <c r="E12" s="34" t="n">
-        <v>18.102</v>
-      </c>
-      <c r="F12" s="34" t="n">
-        <v>4.954</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TDY</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Teledyne Technologies Incorpora</t>
-        </is>
-      </c>
-      <c r="C13" s="33" t="n">
-        <v>28335362048</v>
-      </c>
-      <c r="D13" s="34" t="n">
-        <v>30.967594</v>
-      </c>
-      <c r="E13" s="34" t="n">
-        <v>19.626</v>
-      </c>
-      <c r="F13" s="34" t="n">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Peer median</t>
-        </is>
-      </c>
-      <c r="D15" s="35">
-        <f>MEDIAN(D6:D13)</f>
-        <v/>
-      </c>
-      <c r="E15" s="35">
-        <f>MEDIAN(E6:E13)</f>
-        <v/>
-      </c>
-      <c r="F15" s="35">
-        <f>MEDIAN(F6:F13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Peer mean</t>
-        </is>
-      </c>
-      <c r="D16" s="35">
-        <f>AVERAGE(D6:D13)</f>
-        <v/>
-      </c>
-      <c r="E16" s="35">
-        <f>AVERAGE(E6:E13)</f>
-        <v/>
-      </c>
-      <c r="F16" s="35">
-        <f>AVERAGE(F6:F13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Target percentile vs peers</t>
-        </is>
-      </c>
-      <c r="D17" s="36" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="E17" s="36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F17" s="36" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -152,6 +152,8 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -594,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -619,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-06 04:16 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-06 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -639,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.831</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -655,7 +657,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -732,64 +734,79 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>comps_percentile</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>dcf_margin</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Normalized (intrinsic − market) / market, clipped ±50%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Honest caveats (read before acting)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
-        </is>
-      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -799,6 +816,7 @@
   <mergeCells count="11">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
@@ -807,7 +825,6 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -874,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0453600025177002</v>
+        <v>0.04535999774932861</v>
       </c>
     </row>
     <row r="6">
@@ -1429,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1515,56 +1532,254 @@
         <v>1.28</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Broadridge Financial Solutions,</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>17503725568</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>16.186094</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>11.695</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>2.814</v>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>16996318208</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>16.204628</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>11.383</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>0.985</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FLEX</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Flex Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>55660134400</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>65.48276</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>28.027</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>2.068</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GIB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CGI Inc.</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>14089780224</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>12.2105255</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>6.088</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>1.089</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HPQ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HP Inc.</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>23393490944</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>9.474073000000001</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>6.484</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>0.532</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gartner, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>10981448704</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>16.20751</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>9.476000000000001</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>1.957</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NTAP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NetApp, Inc.</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>33084000256</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>26.305511</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>16.786</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>4.593</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TDY</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Teledyne Technologies Incorpora</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>27902650368</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>30.494684</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>19.409</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>4.796</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D7" s="33">
-        <f>MEDIAN(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E7" s="33">
-        <f>MEDIAN(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F7" s="33">
-        <f>MEDIAN(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="D15" s="35">
+        <f>MEDIAN(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E15" s="35">
+        <f>MEDIAN(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="35">
+        <f>MEDIAN(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D8" s="33">
-        <f>AVERAGE(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E8" s="33">
-        <f>AVERAGE(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F8" s="33">
-        <f>AVERAGE(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="D16" s="35">
+        <f>AVERAGE(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E16" s="35">
+        <f>AVERAGE(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F16" s="35">
+        <f>AVERAGE(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="34" t="n"/>
-      <c r="F9" s="34" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D17" s="36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="E17" s="36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F17" s="36" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-06 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-07 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -1694,10 +1694,10 @@
         <v>26.305511</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>16.786</v>
+        <v>16.919</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.593</v>
+        <v>4.603</v>
       </c>
     </row>
     <row r="13">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-07 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-08 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.831</v>
+        <v>0.832</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>299.61</v>
+        <v>298.48</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>124.43</v>
+        <v>122.31</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.408</v>
+        <v>1.44</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.82</v>
+        <v>0.826</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04552000045776367</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125785467.2988829</v>
+        <v>125785460.8126891</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>124.43</v>
+        <v>122.31</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>15651485696</v>
+        <v>15384819712</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.39</v>
+        <v>11.2</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>9.23</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>17503725568</v>
+        <v>17233664000</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>16.186094</v>
+        <v>15.936363</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>11.695</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>16996318208</v>
+        <v>17489446912</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>16.204628</v>
+        <v>16.674786</v>
       </c>
       <c r="E7" s="34" t="n">
         <v>11.383</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>55660134400</v>
+        <v>55483686912</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>65.48276</v>
+        <v>65.27518000000001</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>28.027</v>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>14089780224</v>
+        <v>13874077696</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>12.2105255</v>
+        <v>12.023593</v>
       </c>
       <c r="E9" s="34" t="n">
         <v>6.088</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>23393490944</v>
+        <v>23114561536</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.474073000000001</v>
+        <v>9.361110999999999</v>
       </c>
       <c r="E10" s="34" t="n">
         <v>6.484</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>10981448704</v>
+        <v>10795992064</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>16.20751</v>
+        <v>15.933795</v>
       </c>
       <c r="E11" s="34" t="n">
         <v>9.476000000000001</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>33084000256</v>
+        <v>33939621888</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>26.305511</v>
+        <v>26.985826</v>
       </c>
       <c r="E12" s="34" t="n">
         <v>16.919</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>27902650368</v>
+        <v>28183404544</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>30.494684</v>
+        <v>30.80152</v>
       </c>
       <c r="E13" s="34" t="n">
         <v>19.409</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-08 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-09 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>298.48</v>
+        <v>299.9</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>122.31</v>
+        <v>122.37</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.44</v>
+        <v>1.451</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04532000064849853</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125785460.8126891</v>
+        <v>125785467.1569829</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>122.31</v>
+        <v>122.37</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>15384819712</v>
+        <v>15392367616</v>
       </c>
       <c r="D5" s="32" t="n">
         <v>11.2</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.23</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>17233664000</v>
+        <v>17353949184</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>15.936363</v>
+        <v>16.030449</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>11.695</v>
+        <v>11.54</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.814</v>
+        <v>2.777</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>17489446912</v>
+        <v>16963102720</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>16.674786</v>
+        <v>16.17296</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.383</v>
+        <v>11.497</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.985</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>55483686912</v>
+        <v>53417902080</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>65.27518000000001</v>
+        <v>62.84483</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>28.027</v>
+        <v>27.833</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.068</v>
+        <v>2.054</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>13874077696</v>
+        <v>14049990656</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>12.023593</v>
+        <v>12.198181</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>6.088</v>
+        <v>6.037</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.089</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>23114561536</v>
+        <v>22337216512</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.361110999999999</v>
+        <v>9.046296</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>6.484</v>
+        <v>6.446</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.532</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>10795992064</v>
+        <v>10465249280</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>15.933795</v>
+        <v>15.445652</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>9.476000000000001</v>
+        <v>9.292999999999999</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>1.957</v>
+        <v>1.919</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>33939621888</v>
+        <v>31836006400</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>26.985826</v>
+        <v>25.589764</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>16.919</v>
+        <v>17.259</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.603</v>
+        <v>4.695</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>28183404544</v>
+        <v>28270735360</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>30.80152</v>
+        <v>30.943968</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.409</v>
+        <v>19.714</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>4.796</v>
+        <v>4.871</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-09 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-11 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.832</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>299.9</v>
+        <v>300.18</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>122.37</v>
+        <v>123.065</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.451</v>
+        <v>1.439</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.826</v>
+        <v>0.824</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.667</v>
+        <v>0.611</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04532000064849853</v>
+        <v>0.04527999877929687</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125785467.1569829</v>
+        <v>125785467.3871531</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>122.37</v>
+        <v>123.065</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>15392367616</v>
+        <v>15479788544</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.2</v>
+        <v>11.26</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.140000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>17353949184</v>
+        <v>16934687744</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>16.030449</v>
+        <v>15.676659</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>11.54</v>
+        <v>11.373</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.777</v>
+        <v>2.737</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>16963102720</v>
+        <v>16468697088</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>16.17296</v>
+        <v>15.701584</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.497</v>
+        <v>11.142</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.995</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>53417902080</v>
+        <v>54319190016</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>62.84483</v>
+        <v>63.6309</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>27.833</v>
+        <v>25.817</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.054</v>
+        <v>1.905</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>14049990656</v>
+        <v>14058366976</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>12.198181</v>
+        <v>12.205454</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>6.037</v>
+        <v>6.057</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.08</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>22337216512</v>
+        <v>22314352640</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.046296</v>
+        <v>9.037037</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>6.446</v>
+        <v>6.312</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.529</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>10465249280</v>
+        <v>10000269312</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>15.445652</v>
+        <v>14.759388</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>9.292999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>1.919</v>
+        <v>1.863</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>31836006400</v>
+        <v>31489953792</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>25.589764</v>
+        <v>25.311607</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>17.259</v>
+        <v>16.256</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.695</v>
+        <v>4.422</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>28270735360</v>
+        <v>28880193536</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>30.943968</v>
+        <v>31.611055</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.714</v>
+        <v>19.382</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>4.871</v>
+        <v>4.789</v>
       </c>
     </row>
     <row r="15">
@@ -1772,7 +1772,7 @@
         <v>0.167</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="36" t="n">
         <v>0.5</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -20,11 +20,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -126,22 +126,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,9 +149,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -596,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -621,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-11 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-18 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.697</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -657,7 +656,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -672,8 +671,10 @@
           <t>DCF intrinsic value / share</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>300.18</v>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>123.065</v>
+        <v>107.055</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -702,8 +703,10 @@
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>1.439</v>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -726,8 +729,8 @@
           <t>value_score</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>0.824</v>
+      <c r="B13" s="8" t="n">
+        <v>0.868</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -737,7 +740,7 @@
           <t>comps_percentile</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="8" t="n">
         <v>0.611</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -746,67 +749,52 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>dcf_margin</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Normalized (intrinsic − market) / market, clipped ±50%</t>
-        </is>
-      </c>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Honest caveats (read before acting)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Honest caveats (read before acting)</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -816,7 +804,6 @@
   <mergeCells count="11">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
@@ -825,6 +812,7 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -890,8 +878,8 @@
           <t>Risk-free rate (10y Treasury)</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
-        <v>0.04527999877929687</v>
+      <c r="B5" s="9" t="n">
+        <v>0.04438000202178955</v>
       </c>
     </row>
     <row r="6">
@@ -900,7 +888,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="9" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -910,7 +898,7 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="10" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -920,7 +908,7 @@
           <t>Credit spread over risk-free</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="9" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -930,7 +918,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="9" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -940,7 +928,7 @@
           <t>Equity weight (cap structure)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="11" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -950,7 +938,7 @@
           <t>FCF growth (flat, faded avg)</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="9" t="n">
         <v>0.0725</v>
       </c>
     </row>
@@ -960,7 +948,7 @@
           <t>Terminal growth rate</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="9" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -970,7 +958,7 @@
           <t>Latest FCF ($, base year)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="12" t="n">
         <v>1625000000</v>
       </c>
     </row>
@@ -980,7 +968,7 @@
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="13">
         <f>B5+B7*B6</f>
         <v/>
       </c>
@@ -991,18 +979,18 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="13">
         <f>(B5+B8)*(1-B9)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="15">
         <f>B10*B15+(1-B10)*B16</f>
         <v/>
       </c>
@@ -1049,23 +1037,23 @@
           <t>Projected FCF</t>
         </is>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="16">
         <f>$B$13*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="16">
         <f>B22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="16">
         <f>C22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="16">
         <f>D22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="16">
         <f>E22*(1+$B$11)</f>
         <v/>
       </c>
@@ -1076,23 +1064,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="17">
         <f>1/(1+$B$17)^1</f>
         <v/>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="17">
         <f>1/(1+$B$17)^2</f>
         <v/>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="17">
         <f>1/(1+$B$17)^3</f>
         <v/>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="17">
         <f>1/(1+$B$17)^4</f>
         <v/>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="17">
         <f>1/(1+$B$17)^5</f>
         <v/>
       </c>
@@ -1103,23 +1091,23 @@
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="16">
         <f>B22*B23</f>
         <v/>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="16">
         <f>C22*C23</f>
         <v/>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="16">
         <f>D22*D23</f>
         <v/>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="16">
         <f>E22*E23</f>
         <v/>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="16">
         <f>F22*F23</f>
         <v/>
       </c>
@@ -1130,7 +1118,7 @@
           <t>Sum of PV (explicit 5y)</t>
         </is>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="16">
         <f>SUM(B24:F24)</f>
         <v/>
       </c>
@@ -1141,7 +1129,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="16">
         <f>F22*(1+B12)/(B17-B12)</f>
         <v/>
       </c>
@@ -1152,18 +1140,18 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="16">
         <f>B27/(1+B17)^5</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="19">
         <f>B26+B28</f>
         <v/>
       </c>
@@ -1188,7 +1176,7 @@
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n">
+      <c r="B32" s="12" t="n">
         <v>6944000000</v>
       </c>
     </row>
@@ -1198,7 +1186,7 @@
           <t>Plus: cash &amp; ST investments</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
+      <c r="B33" s="12" t="n">
         <v>457000000</v>
       </c>
     </row>
@@ -1208,7 +1196,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="16">
         <f>B29-B32+B33</f>
         <v/>
       </c>
@@ -1219,17 +1207,17 @@
           <t>Diluted shares outstanding</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
-        <v>125785467.3871531</v>
+      <c r="B35" s="20" t="n">
+        <v>125785460.7071132</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Intrinsic per share</t>
         </is>
       </c>
-      <c r="B36" s="22">
+      <c r="B36" s="21">
         <f>B34/B35</f>
         <v/>
       </c>
@@ -1240,17 +1228,17 @@
           <t>Current market price</t>
         </is>
       </c>
-      <c r="B37" s="23" t="n">
-        <v>123.065</v>
+      <c r="B37" s="22" t="n">
+        <v>107.055</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="23">
         <f>(B36-B37)/B37</f>
         <v/>
       </c>
@@ -1270,158 +1258,158 @@
       <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>WACC ↓ / TermG →</t>
         </is>
       </c>
-      <c r="B42" s="26">
+      <c r="B42" s="25">
         <f>$B$12+-0.01</f>
         <v/>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="25">
         <f>$B$12+-0.005</f>
         <v/>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="25">
         <f>$B$12+0.0</f>
         <v/>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="25">
         <f>$B$12+0.005</f>
         <v/>
       </c>
-      <c r="F42" s="26">
+      <c r="F42" s="25">
         <f>$B$12+0.01</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="26">
+      <c r="A43" s="25">
         <f>$B$17+-0.01</f>
         <v/>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A43-B$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A43-C$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D43" s="27">
+      <c r="D43" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A43-D$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E43" s="27">
+      <c r="E43" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A43-E$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F43" s="27">
+      <c r="F43" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A43-F$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="26">
+      <c r="A44" s="25">
         <f>$B$17+-0.005</f>
         <v/>
       </c>
-      <c r="B44" s="27">
+      <c r="B44" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A44-B$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A44-C$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D44" s="27">
+      <c r="D44" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A44-D$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A44-E$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F44" s="27">
+      <c r="F44" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A44-F$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="26">
+      <c r="A45" s="25">
         <f>$B$17+0.0</f>
         <v/>
       </c>
-      <c r="B45" s="27">
+      <c r="B45" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A45-B$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A45-C$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D45" s="28">
+      <c r="D45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A45-D$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A45-E$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F45" s="27">
+      <c r="F45" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A45-F$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="26">
+      <c r="A46" s="25">
         <f>$B$17+0.005</f>
         <v/>
       </c>
-      <c r="B46" s="27">
+      <c r="B46" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A46-B$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A46-C$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D46" s="27">
+      <c r="D46" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A46-D$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E46" s="27">
+      <c r="E46" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A46-E$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F46" s="27">
+      <c r="F46" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A46-F$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="26">
+      <c r="A47" s="25">
         <f>$B$17+0.01</f>
         <v/>
       </c>
-      <c r="B47" s="27">
+      <c r="B47" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A47-B$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A47-C$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A47-D$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E47" s="27">
+      <c r="E47" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A47-E$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F47" s="27">
+      <c r="F47" s="26">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A47-F$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
@@ -1477,59 +1465,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>P/E (TTM)</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>EV/Revenue</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>LDOS</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Leidos Holdings, Inc.</t>
         </is>
       </c>
-      <c r="C5" s="31" t="n">
-        <v>15479788544</v>
-      </c>
-      <c r="D5" s="32" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="E5" s="32" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="F5" s="32" t="n">
-        <v>1.26</v>
+      <c r="C5" s="30" t="n">
+        <v>13465962496</v>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="E5" s="31" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="F5" s="31" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
@@ -1543,17 +1531,17 @@
           <t>Broadridge Financial Solutions,</t>
         </is>
       </c>
-      <c r="C6" s="33" t="n">
-        <v>16934687744</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <v>15.676659</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <v>11.373</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>2.737</v>
+      <c r="C6" s="32" t="n">
+        <v>15838826496</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>14.646524</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>11.205</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>2.696</v>
       </c>
     </row>
     <row r="7">
@@ -1567,17 +1555,17 @@
           <t>CDW Corporation</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n">
-        <v>16468697088</v>
-      </c>
-      <c r="D7" s="34" t="n">
-        <v>15.701584</v>
-      </c>
-      <c r="E7" s="34" t="n">
-        <v>11.142</v>
-      </c>
-      <c r="F7" s="34" t="n">
-        <v>0.964</v>
+      <c r="C7" s="32" t="n">
+        <v>16394600448</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>15.630938</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>11.193</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>0.969</v>
       </c>
     </row>
     <row r="8">
@@ -1591,17 +1579,17 @@
           <t>Flex Ltd.</t>
         </is>
       </c>
-      <c r="C8" s="33" t="n">
-        <v>54319190016</v>
-      </c>
-      <c r="D8" s="34" t="n">
-        <v>63.6309</v>
-      </c>
-      <c r="E8" s="34" t="n">
-        <v>25.817</v>
-      </c>
-      <c r="F8" s="34" t="n">
-        <v>1.905</v>
+      <c r="C8" s="32" t="n">
+        <v>53144944640</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>61.989315</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>2.003</v>
       </c>
     </row>
     <row r="9">
@@ -1615,16 +1603,16 @@
           <t>CGI Inc.</t>
         </is>
       </c>
-      <c r="C9" s="33" t="n">
-        <v>14058366976</v>
-      </c>
-      <c r="D9" s="34" t="n">
-        <v>12.205454</v>
-      </c>
-      <c r="E9" s="34" t="n">
-        <v>6.057</v>
-      </c>
-      <c r="F9" s="34" t="n">
+      <c r="C9" s="32" t="n">
+        <v>12769387520</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>11.106558</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>6.056</v>
+      </c>
+      <c r="F9" s="33" t="n">
         <v>1.083</v>
       </c>
     </row>
@@ -1639,17 +1627,17 @@
           <t>HP Inc.</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n">
-        <v>22314352640</v>
-      </c>
-      <c r="D10" s="34" t="n">
-        <v>9.037037</v>
-      </c>
-      <c r="E10" s="34" t="n">
-        <v>6.312</v>
-      </c>
-      <c r="F10" s="34" t="n">
-        <v>0.518</v>
+      <c r="C10" s="32" t="n">
+        <v>21367822336</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>8.653703999999999</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>6.234</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>0.512</v>
       </c>
     </row>
     <row r="11">
@@ -1663,17 +1651,17 @@
           <t>Gartner, Inc.</t>
         </is>
       </c>
-      <c r="C11" s="33" t="n">
-        <v>10000269312</v>
-      </c>
-      <c r="D11" s="34" t="n">
-        <v>14.759388</v>
-      </c>
-      <c r="E11" s="34" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="F11" s="34" t="n">
-        <v>1.863</v>
+      <c r="C11" s="32" t="n">
+        <v>8502220288</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>12.560831</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>8.385999999999999</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>1.732</v>
       </c>
     </row>
     <row r="12">
@@ -1687,17 +1675,17 @@
           <t>NetApp, Inc.</t>
         </is>
       </c>
-      <c r="C12" s="33" t="n">
-        <v>31489953792</v>
-      </c>
-      <c r="D12" s="34" t="n">
-        <v>25.311607</v>
-      </c>
-      <c r="E12" s="34" t="n">
-        <v>16.256</v>
-      </c>
-      <c r="F12" s="34" t="n">
-        <v>4.422</v>
+      <c r="C12" s="32" t="n">
+        <v>31276656640</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>25.140158</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>16.318</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>4.439</v>
       </c>
     </row>
     <row r="13">
@@ -1711,17 +1699,17 @@
           <t>Teledyne Technologies Incorpora</t>
         </is>
       </c>
-      <c r="C13" s="33" t="n">
-        <v>28880193536</v>
-      </c>
-      <c r="D13" s="34" t="n">
-        <v>31.611055</v>
-      </c>
-      <c r="E13" s="34" t="n">
-        <v>19.382</v>
-      </c>
-      <c r="F13" s="34" t="n">
-        <v>4.789</v>
+      <c r="C13" s="32" t="n">
+        <v>28620982272</v>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>31.327335</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>20.247</v>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>5.003</v>
       </c>
     </row>
     <row r="15">
@@ -1730,15 +1718,15 @@
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="34">
         <f>MEDIAN(D6:D13)</f>
         <v/>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="34">
         <f>MEDIAN(E6:E13)</f>
         <v/>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="34">
         <f>MEDIAN(F6:F13)</f>
         <v/>
       </c>
@@ -1749,15 +1737,15 @@
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="34">
         <f>AVERAGE(D6:D13)</f>
         <v/>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="34">
         <f>AVERAGE(E6:E13)</f>
         <v/>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="34">
         <f>AVERAGE(F6:F13)</f>
         <v/>
       </c>
@@ -1768,13 +1756,13 @@
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D17" s="36" t="n">
+      <c r="D17" s="35" t="n">
         <v>0.167</v>
       </c>
-      <c r="E17" s="36" t="n">
+      <c r="E17" s="35" t="n">
         <v>0.5</v>
       </c>
-      <c r="F17" s="36" t="n">
+      <c r="F17" s="35" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-18 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.697</v>
+        <v>0.702</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>107.055</v>
+        <v>101.135</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.868</v>
+        <v>0.885</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04438000202178955</v>
+        <v>0.04372000217437744</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>125785460.7071132</v>
+        <v>125785462.6785979</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>107.055</v>
+        <v>101.135</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>13465962496</v>
+        <v>12721312768</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.789999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>8.66</v>
+        <v>7.95</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>15838826496</v>
+        <v>16153994240</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.646524</v>
+        <v>14.937967</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>11.205</v>
+        <v>10.705</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.696</v>
+        <v>2.576</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>16394600448</v>
+        <v>16651383808</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>15.630938</v>
+        <v>15.875761</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>11.193</v>
+        <v>11.06</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.969</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>53144944640</v>
+        <v>55344971776</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>61.989315</v>
+        <v>65.10991</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>27.14</v>
+        <v>29.692</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.003</v>
+        <v>2.191</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>12769387520</v>
+        <v>13296078848</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>11.106558</v>
+        <v>11.779222</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>6.056</v>
+        <v>5.727</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.083</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>21367822336</v>
+        <v>20659066880</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>8.653703999999999</v>
+        <v>8.366667</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>6.234</v>
+        <v>5.968</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.512</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>8502220288</v>
+        <v>8911798272</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>12.560831</v>
+        <v>13.152915</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>8.385999999999999</v>
+        <v>7.604</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.732</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>31276656640</v>
+        <v>29483988992</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>25.140158</v>
+        <v>23.699213</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.318</v>
+        <v>15.624</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>4.439</v>
+        <v>4.251</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>28620982272</v>
+        <v>29123885056</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>31.327335</v>
+        <v>31.81326</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>20.247</v>
+        <v>20.16</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>5.003</v>
+        <v>4.981</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-27 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>101.135</v>
+        <v>101.76</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.885</v>
+        <v>0.883</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04372</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>125785462.6785979</v>
+        <v>125785469.1823899</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>101.135</v>
+        <v>101.76</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>12721312768</v>
+        <v>12799929344</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.25</v>
+        <v>9.31</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>7.95</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>16153994240</v>
+        <v>15952747520</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.937967</v>
+        <v>14.75187</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>10.705</v>
+        <v>10.815</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.576</v>
+        <v>2.602</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>16651383808</v>
+        <v>17029534720</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>15.875761</v>
+        <v>16.236298</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>11.06</v>
+        <v>11.4</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.957</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>55344971776</v>
+        <v>53749350400</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>65.10991</v>
+        <v>62.961372</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>29.692</v>
+        <v>27.099</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.191</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>13296078848</v>
+        <v>13499215872</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>11.779222</v>
+        <v>11.981412</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>5.727</v>
+        <v>5.886</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.024</v>
+        <v>1.053</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>20659066880</v>
+        <v>20924278784</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>8.366667</v>
+        <v>8.474073000000001</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>5.968</v>
+        <v>5.96</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.49</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>8911798272</v>
+        <v>9035827200</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>13.152915</v>
+        <v>13.335969</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>7.604</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.57</v>
+        <v>1.656</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>29483988992</v>
+        <v>29867991040</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>23.699213</v>
+        <v>23.970125</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>15.624</v>
+        <v>15.402</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>4.251</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>29123885056</v>
+        <v>28922814464</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>31.81326</v>
+        <v>31.641663</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>20.16</v>
+        <v>20.073</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>4.981</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-27 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04372</v>
+        <v>0.04372000217437744</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>101.76</v>
+        <v>101.88</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04409999847412109</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>125785469.1823899</v>
+        <v>125785464.3109541</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>101.76</v>
+        <v>101.88</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>12799929344</v>
+        <v>12815023104</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.31</v>
+        <v>9.32</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>8.039999999999999</v>
+        <v>7.97</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>15952747520</v>
+        <v>15731842048</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.75187</v>
+        <v>14.547593</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>10.815</v>
+        <v>10.651</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.602</v>
+        <v>2.563</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>17029534720</v>
+        <v>18045173760</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>16.236298</v>
+        <v>17.204628</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>11.4</v>
+        <v>11.82</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.987</v>
+        <v>1.023</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>53749350400</v>
+        <v>59237863424</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>62.961372</v>
+        <v>69.39055999999999</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>27.099</v>
+        <v>29.386</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2</v>
+        <v>2.169</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>13499215872</v>
+        <v>13424872448</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>11.981412</v>
+        <v>11.871297</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>5.886</v>
+        <v>5.834</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.053</v>
+        <v>1.043</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>20924278784</v>
+        <v>20160653312</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>8.474073000000001</v>
+        <v>8.164815000000001</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>5.96</v>
+        <v>5.914</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.489</v>
+        <v>0.485</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>9035827200</v>
+        <v>8706758656</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>13.335969</v>
+        <v>12.850296</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>8.021000000000001</v>
+        <v>7.913</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.656</v>
+        <v>1.634</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>29867991040</v>
+        <v>30106996736</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>23.970125</v>
+        <v>24.161934</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>15.402</v>
+        <v>15.673</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>4.19</v>
+        <v>4.264</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>28922814464</v>
+        <v>30822772736</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>31.641663</v>
+        <v>33.686077</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>20.073</v>
+        <v>20.583</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>4.96</v>
+        <v>5.086</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.702</v>
+        <v>0.695</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>101.88</v>
+        <v>108.84</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.883</v>
+        <v>0.863</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04409999847412109</v>
+        <v>0.044849997</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>125785464.3109541</v>
+        <v>125785463.5795663</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>101.88</v>
+        <v>108.84</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>12815023104</v>
+        <v>13690489856</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.32</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>7.97</v>
+        <v>8.41</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>15731842048</v>
+        <v>16649011200</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.547593</v>
+        <v>15.379273</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>10.651</v>
+        <v>11.21</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.563</v>
+        <v>2.697</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>18045173760</v>
+        <v>17038476288</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>17.204628</v>
+        <v>16.244823</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>11.82</v>
+        <v>11.405</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.023</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>59237863424</v>
+        <v>50142240768</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>69.39055999999999</v>
+        <v>58.736053</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>29.386</v>
+        <v>25.348</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.169</v>
+        <v>1.871</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>13424872448</v>
+        <v>13922245632</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>11.871297</v>
+        <v>12.311111</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>5.834</v>
+        <v>6.031</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.043</v>
+        <v>1.079</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>20160653312</v>
+        <v>20055482368</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>8.164815000000001</v>
+        <v>8.122222000000001</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>5.914</v>
+        <v>5.776</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.485</v>
+        <v>0.474</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>8706758656</v>
+        <v>9126882304</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>12.850296</v>
+        <v>13.483681</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>7.913</v>
+        <v>8.089</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.634</v>
+        <v>1.671</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>30106996736</v>
+        <v>30204973056</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>24.161934</v>
+        <v>24.27874</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>15.673</v>
+        <v>15.581</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>4.264</v>
+        <v>4.239</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>30822772736</v>
+        <v>30210304000</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>33.686077</v>
+        <v>33</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>20.583</v>
+        <v>20.91</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>5.086</v>
+        <v>5.167</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-04 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
         <v>17038476288</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>16.244823</v>
+        <v>16.22506</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>11.405</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-04 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.044849997</v>
+        <v>0.04485000133514404</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-06 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.695</v>
+        <v>0.694</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>108.84</v>
+        <v>109.86</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.863</v>
+        <v>0.86</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04485000133514404</v>
+        <v>0.04480999946594239</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>125785463.5795663</v>
+        <v>125785462.5159294</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>108.84</v>
+        <v>109.86</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>13690489856</v>
+        <v>13818790912</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.960000000000001</v>
+        <v>10.05</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>8.41</v>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>16649011200</v>
+        <v>16716093440</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>15.379273</v>
+        <v>15.441239</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>11.21</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>17038476288</v>
+        <v>17198807040</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>16.22506</v>
+        <v>16.377737</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>11.405</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>50142240768</v>
+        <v>51230019584</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>58.736053</v>
+        <v>60.010258</v>
       </c>
       <c r="E8" s="33" t="n">
         <v>25.348</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>13922245632</v>
+        <v>13900255232</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>12.311111</v>
+        <v>12.291666</v>
       </c>
       <c r="E9" s="33" t="n">
         <v>6.031</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>20055482368</v>
+        <v>20590477312</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>8.122222000000001</v>
+        <v>8.338888000000001</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>5.776</v>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>9126882304</v>
+        <v>9103113216</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>13.483681</v>
+        <v>13.4485655</v>
       </c>
       <c r="E11" s="33" t="n">
         <v>8.089</v>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>30204973056</v>
+        <v>31758620672</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>24.27874</v>
+        <v>25.527561</v>
       </c>
       <c r="E12" s="33" t="n">
         <v>15.581</v>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>30210304000</v>
+        <v>30451445760</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>33</v>
+        <v>33.26341</v>
       </c>
       <c r="E13" s="33" t="n">
         <v>20.91</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-06 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.694</v>
+        <v>0.696</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>109.86</v>
+        <v>108.11</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.86</v>
+        <v>0.865</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04480999946594239</v>
+        <v>0.04525000095367432</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>125785462.5159294</v>
+        <v>125785466.2103413</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>109.86</v>
+        <v>108.11</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>13818790912</v>
+        <v>13598666752</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>10.05</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>8.41</v>
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>16716093440</v>
+        <v>17233086464</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>15.441239</v>
+        <v>15.935828</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>11.21</v>
+        <v>11.264</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.697</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>17198807040</v>
+        <v>17578874880</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>16.377737</v>
+        <v>16.76005</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>11.405</v>
+        <v>11.457</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.987</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>51230019584</v>
+        <v>48458682368</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>60.010258</v>
+        <v>56.763947</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>25.348</v>
+        <v>25.667</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>1.871</v>
+        <v>1.894</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>13900255232</v>
+        <v>14249987072</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>12.291666</v>
+        <v>12.624304</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>6.031</v>
+        <v>6.021</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.079</v>
+        <v>1.077</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>20590477312</v>
+        <v>20988297216</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>8.338888000000001</v>
+        <v>8.5</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>5.776</v>
+        <v>5.906</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.474</v>
+        <v>0.485</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>9103113216</v>
+        <v>9539304448</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>13.4485655</v>
+        <v>14.079051</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>8.089</v>
+        <v>8.029</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.671</v>
+        <v>1.658</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>31758620672</v>
+        <v>32793077760</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>25.527561</v>
+        <v>26.359056</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>15.581</v>
+        <v>16.556</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>4.239</v>
+        <v>4.504</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>30451445760</v>
+        <v>29666400256</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>33.26341</v>
+        <v>32.48808</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>20.91</v>
+        <v>20.997</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>5.167</v>
+        <v>5.188</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.696</v>
+        <v>0.735</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>108.11</v>
+        <v>106.395</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.865</v>
+        <v>0.87</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.611</v>
+        <v>0.667</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04525000095367432</v>
+        <v>0.04550000190734863</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>125785466.2103413</v>
+        <v>125785457.4369096</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>108.11</v>
+        <v>106.395</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>13598666752</v>
+        <v>13382943744</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.890000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>8.41</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>17233086464</v>
+        <v>17426235392</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>15.935828</v>
+        <v>16.114437</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>11.264</v>
+        <v>11.808</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.71</v>
+        <v>2.841</v>
       </c>
     </row>
     <row r="7">
@@ -1556,13 +1556,13 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>17578874880</v>
+        <v>17133654016</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>16.76005</v>
+        <v>16.335567</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>11.457</v>
+        <v>11.467</v>
       </c>
       <c r="F7" s="33" t="n">
         <v>0.992</v>
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>48458682368</v>
+        <v>43845840896</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>56.763947</v>
+        <v>51.360516</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>25.667</v>
+        <v>22.549</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>1.894</v>
+        <v>1.664</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>14249987072</v>
+        <v>14283494400</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>12.624304</v>
+        <v>12.630556</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>6.021</v>
+        <v>6.15</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.077</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>20988297216</v>
+        <v>22968238080</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>8.5</v>
+        <v>9.301850999999999</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>5.906</v>
+        <v>6.205</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.485</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>9539304448</v>
+        <v>9442560000</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>14.079051</v>
+        <v>13.936265</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>8.029</v>
+        <v>8.417999999999999</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.658</v>
+        <v>1.738</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>32793077760</v>
+        <v>32340502528</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>26.359056</v>
+        <v>25.954403</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.556</v>
+        <v>16.155</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>4.504</v>
+        <v>4.395</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>29666400256</v>
+        <v>29396299776</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>32.48808</v>
+        <v>32.12709</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>20.997</v>
+        <v>20.27</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>5.188</v>
+        <v>5.009</v>
       </c>
     </row>
     <row r="15">
@@ -1760,7 +1760,7 @@
         <v>0.167</v>
       </c>
       <c r="E17" s="35" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="F17" s="35" t="n">
         <v>0.5</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.735</v>
+        <v>0.697</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>106.395</v>
+        <v>106.48</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.667</v>
+        <v>0.611</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04550000190734863</v>
+        <v>0.04540999889373779</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>125785457.4369096</v>
+        <v>125785465.3643877</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>106.395</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>13382943744</v>
+        <v>13393636352</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>8.390000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="6">
@@ -1528,20 +1528,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions,</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>17426235392</v>
+        <v>17338335232</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>16.114437</v>
+        <v>16.033155</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>11.808</v>
+        <v>11.601</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.841</v>
+        <v>2.791</v>
       </c>
     </row>
     <row r="7">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>17133654016</v>
+        <v>17021870080</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>16.335567</v>
+        <v>16.22899</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>11.467</v>
+        <v>11.396</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.992</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>43845840896</v>
+        <v>43691954176</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>51.360516</v>
+        <v>51.400864</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>22.549</v>
+        <v>22.217</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>1.664</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="9">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CGI Inc.</t>
+          <t>GIB</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>14283494400</v>
+        <v>14265694208</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>12.630556</v>
+        <v>12.614815</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>6.15</v>
+        <v>6.148</v>
       </c>
       <c r="F9" s="33" t="n">
         <v>1.1</v>
@@ -1624,20 +1624,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HP Inc.</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>22968238080</v>
+        <v>22716743680</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>9.301850999999999</v>
+        <v>8.935252</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>6.205</v>
+        <v>6.341</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.509</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>9442560000</v>
+        <v>9385985024</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>13.936265</v>
+        <v>13.852767</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>8.417999999999999</v>
+        <v>8.282999999999999</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.738</v>
+        <v>1.711</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>32340502528</v>
+        <v>32107358208</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>25.954403</v>
+        <v>25.848581</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.155</v>
+        <v>16.59</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>4.395</v>
+        <v>4.514</v>
       </c>
     </row>
     <row r="13">
@@ -1696,20 +1696,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Teledyne Technologies Incorpora</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>29396299776</v>
+        <v>29443092480</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>32.12709</v>
+        <v>32.161945</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>20.27</v>
+        <v>20.411</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>5.009</v>
+        <v>5.043</v>
       </c>
     </row>
     <row r="15">
@@ -1760,7 +1760,7 @@
         <v>0.167</v>
       </c>
       <c r="E17" s="35" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="35" t="n">
         <v>0.5</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-19 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>Broadridge Financial Solutions,</t>
         </is>
       </c>
       <c r="C6" s="32" t="n">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="C7" s="32" t="n">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GIB</t>
+          <t>CGI Inc.</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
@@ -1624,14 +1624,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>HP Inc.</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
         <v>22716743680</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>8.935252</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>6.341</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>Teledyne Technologies Incorpora</t>
         </is>
       </c>
       <c r="C13" s="32" t="n">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-19 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-20 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>106.48</v>
+        <v>107.155</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.87</v>
+        <v>0.868</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04540999889373779</v>
+        <v>0.04604000091552735</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>125785465.3643877</v>
+        <v>125785463.2261677</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>106.48</v>
+        <v>107.155</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>13393636352</v>
+        <v>13478541312</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.75</v>
+        <v>9.81</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>8.289999999999999</v>
@@ -1531,11 +1531,9 @@
           <t>Broadridge Financial Solutions,</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n">
-        <v>17338335232</v>
-      </c>
+      <c r="C6" s="32" t="n"/>
       <c r="D6" s="33" t="n">
-        <v>16.033155</v>
+        <v>16.120855</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>11.601</v>
@@ -1555,11 +1553,9 @@
           <t>CDW Corporation</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n">
-        <v>17021870080</v>
-      </c>
+      <c r="C7" s="32" t="n"/>
       <c r="D7" s="33" t="n">
-        <v>16.22899</v>
+        <v>16.035322</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>11.396</v>
@@ -1580,10 +1576,10 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>43691954176</v>
+        <v>44267188224</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>51.400864</v>
+        <v>52.077587</v>
       </c>
       <c r="E8" s="33" t="n">
         <v>22.217</v>
@@ -1603,11 +1599,9 @@
           <t>CGI Inc.</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
-        <v>14265694208</v>
-      </c>
+      <c r="C9" s="32" t="n"/>
       <c r="D9" s="33" t="n">
-        <v>12.614815</v>
+        <v>12.692593</v>
       </c>
       <c r="E9" s="33" t="n">
         <v>6.148</v>
@@ -1627,11 +1621,9 @@
           <t>HP Inc.</t>
         </is>
       </c>
-      <c r="C10" s="32" t="n">
-        <v>22716743680</v>
-      </c>
+      <c r="C10" s="32" t="n"/>
       <c r="D10" s="33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.042593</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>6.341</v>
@@ -1652,10 +1644,10 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>9385985024</v>
+        <v>9450593280</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>13.852767</v>
+        <v>13.948123</v>
       </c>
       <c r="E11" s="33" t="n">
         <v>8.282999999999999</v>
@@ -1676,10 +1668,10 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>32107358208</v>
+        <v>32034865152</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>25.848581</v>
+        <v>25.79022</v>
       </c>
       <c r="E12" s="33" t="n">
         <v>16.59</v>
@@ -1699,11 +1691,9 @@
           <t>Teledyne Technologies Incorpora</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n">
-        <v>29443092480</v>
-      </c>
+      <c r="C13" s="32" t="n"/>
       <c r="D13" s="33" t="n">
-        <v>32.161945</v>
+        <v>31.828947</v>
       </c>
       <c r="E13" s="33" t="n">
         <v>20.411</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-20 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-21 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.697</v>
+        <v>0.736</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>107.155</v>
+        <v>104.71</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.868</v>
+        <v>0.875</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.611</v>
+        <v>0.667</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04625999927520752</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>125785463.2261677</v>
+        <v>125785466.7558018</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>107.155</v>
+        <v>104.71</v>
       </c>
     </row>
     <row r="38">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>13478541312</v>
+        <v>13170996224</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.81</v>
+        <v>9.58</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>8.289999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>1.15</v>
@@ -1531,15 +1531,17 @@
           <t>Broadridge Financial Solutions,</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n"/>
+      <c r="C6" s="32" t="n">
+        <v>16791270400</v>
+      </c>
       <c r="D6" s="33" t="n">
-        <v>16.120855</v>
+        <v>15.527271</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>11.601</v>
+        <v>11.608</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.791</v>
+        <v>2.793</v>
       </c>
     </row>
     <row r="7">
@@ -1553,15 +1555,17 @@
           <t>CDW Corporation</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n"/>
+      <c r="C7" s="32" t="n">
+        <v>16429731840</v>
+      </c>
       <c r="D7" s="33" t="n">
-        <v>16.035322</v>
+        <v>15.6644335</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>11.396</v>
+        <v>11.188</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.986</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="8">
@@ -1576,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>44267188224</v>
+        <v>46824587264</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>52.077587</v>
+        <v>54.84979</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>22.217</v>
+        <v>22.334</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>1.64</v>
+        <v>1.648</v>
       </c>
     </row>
     <row r="9">
@@ -1599,15 +1603,17 @@
           <t>CGI Inc.</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n"/>
+      <c r="C9" s="32" t="n">
+        <v>14022766592</v>
+      </c>
       <c r="D9" s="33" t="n">
-        <v>12.692593</v>
+        <v>12.4</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>6.148</v>
+        <v>6.157</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.1</v>
+        <v>1.101</v>
       </c>
     </row>
     <row r="10">
@@ -1621,15 +1627,17 @@
           <t>HP Inc.</t>
         </is>
       </c>
-      <c r="C10" s="32" t="n"/>
+      <c r="C10" s="32" t="n">
+        <v>22446958592</v>
+      </c>
       <c r="D10" s="33" t="n">
-        <v>9.042593</v>
+        <v>9.09074</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>6.341</v>
+        <v>6.22</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="11">
@@ -1644,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>9450593280</v>
+        <v>8994122752</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>13.948123</v>
+        <v>13.287547</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>8.282999999999999</v>
+        <v>8.327</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.711</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="12">
@@ -1668,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>32034865152</v>
+        <v>32205318144</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>25.79022</v>
+        <v>25.886616</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.59</v>
+        <v>16.308</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>4.514</v>
+        <v>4.437</v>
       </c>
     </row>
     <row r="13">
@@ -1691,15 +1699,17 @@
           <t>Teledyne Technologies Incorpora</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n"/>
+      <c r="C13" s="32" t="n">
+        <v>30579546112</v>
+      </c>
       <c r="D13" s="33" t="n">
-        <v>31.828947</v>
+        <v>33.437183</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>20.411</v>
+        <v>20.142</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>5.043</v>
+        <v>4.977</v>
       </c>
     </row>
     <row r="15">
@@ -1750,7 +1760,7 @@
         <v>0.167</v>
       </c>
       <c r="E17" s="35" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="F17" s="35" t="n">
         <v>0.5</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-21 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.736</v>
+        <v>0.726</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>104.71</v>
+        <v>115.67</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.875</v>
+        <v>0.844</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04625999927520752</v>
+        <v>0.04647000312805176</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>125785466.7558018</v>
+        <v>125785461.675456</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>104.71</v>
+        <v>115.67</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>13170996224</v>
+        <v>14549604352</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>9.58</v>
+        <v>10.59</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>8.32</v>
+        <v>8.91</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>16791270400</v>
+        <v>18590337024</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>15.527271</v>
+        <v>17.190908</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>11.608</v>
+        <v>12.144</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.793</v>
+        <v>2.922</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>16429731840</v>
+        <v>18827024384</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>15.6644335</v>
+        <v>17.95006</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>11.188</v>
+        <v>12.092</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.968</v>
+        <v>1.046</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>46824587264</v>
+        <v>37937807360</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>54.84979</v>
+        <v>44.439915</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>22.334</v>
+        <v>21.155</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>1.648</v>
+        <v>1.561</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>14022766592</v>
+        <v>15551533056</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>12.4</v>
+        <v>13.650736</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>6.157</v>
+        <v>6.383</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>1.101</v>
+        <v>1.142</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>22446958592</v>
+        <v>26100477952</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>9.09074</v>
+        <v>10.570371</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>6.22</v>
+        <v>7.01</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.51</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>8994122752</v>
+        <v>11084554240</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>13.287547</v>
+        <v>16.375866</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>8.327</v>
+        <v>9.067</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.72</v>
+        <v>1.872</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>32205318144</v>
+        <v>34181167104</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>25.886616</v>
+        <v>27.474804</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>16.308</v>
+        <v>17.698</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>4.437</v>
+        <v>4.815</v>
       </c>
     </row>
     <row r="13">
@@ -1700,16 +1700,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>30579546112</v>
+        <v>29436606464</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>33.437183</v>
+        <v>30.754114</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>20.142</v>
+        <v>19.972</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>4.977</v>
+        <v>4.989</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -20,11 +20,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -126,21 +126,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,9 +150,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -595,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -620,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.726</v>
+        <v>0.836</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -656,7 +657,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -671,10 +672,8 @@
           <t>DCF intrinsic value / share</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B8" s="7" t="n">
+        <v>285.37</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -689,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>115.67</v>
+        <v>115.6</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,10 +702,8 @@
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B10" s="8" t="n">
+        <v>1.469</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -729,7 +726,7 @@
           <t>value_score</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="9" t="n">
         <v>0.844</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
@@ -740,7 +737,7 @@
           <t>comps_percentile</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="9" t="n">
         <v>0.667</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -749,52 +746,67 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>dcf_margin</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Normalized (intrinsic − market) / market, clipped ±50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Honest caveats (read before acting)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
-        </is>
-      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -804,6 +816,7 @@
   <mergeCells count="11">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
@@ -812,7 +825,6 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -878,8 +890,8 @@
           <t>Risk-free rate (10y Treasury)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>0.04647000312805176</v>
+      <c r="B5" s="10" t="n">
+        <v>0.04744999885559082</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +900,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="10" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -898,7 +910,7 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -908,7 +920,7 @@
           <t>Credit spread over risk-free</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -918,7 +930,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="10" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -928,7 +940,7 @@
           <t>Equity weight (cap structure)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -938,7 +950,7 @@
           <t>FCF growth (flat, faded avg)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="10" t="n">
         <v>0.0725</v>
       </c>
     </row>
@@ -948,7 +960,7 @@
           <t>Terminal growth rate</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="10" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -958,7 +970,7 @@
           <t>Latest FCF ($, base year)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>1625000000</v>
       </c>
     </row>
@@ -968,7 +980,7 @@
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="14">
         <f>B5+B7*B6</f>
         <v/>
       </c>
@@ -979,18 +991,18 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="14">
         <f>(B5+B8)*(1-B9)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="16">
         <f>B10*B15+(1-B10)*B16</f>
         <v/>
       </c>
@@ -1037,23 +1049,23 @@
           <t>Projected FCF</t>
         </is>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="17">
         <f>$B$13*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="17">
         <f>B22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <f>C22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="17">
         <f>D22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="17">
         <f>E22*(1+$B$11)</f>
         <v/>
       </c>
@@ -1064,23 +1076,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="18">
         <f>1/(1+$B$17)^1</f>
         <v/>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="18">
         <f>1/(1+$B$17)^2</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="18">
         <f>1/(1+$B$17)^3</f>
         <v/>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="18">
         <f>1/(1+$B$17)^4</f>
         <v/>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="18">
         <f>1/(1+$B$17)^5</f>
         <v/>
       </c>
@@ -1091,23 +1103,23 @@
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="17">
         <f>B22*B23</f>
         <v/>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="17">
         <f>C22*C23</f>
         <v/>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <f>D22*D23</f>
         <v/>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <f>E22*E23</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="17">
         <f>F22*F23</f>
         <v/>
       </c>
@@ -1118,7 +1130,7 @@
           <t>Sum of PV (explicit 5y)</t>
         </is>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <f>SUM(B24:F24)</f>
         <v/>
       </c>
@@ -1129,7 +1141,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="17">
         <f>F22*(1+B12)/(B17-B12)</f>
         <v/>
       </c>
@@ -1140,18 +1152,18 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <f>B27/(1+B17)^5</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="20">
         <f>B26+B28</f>
         <v/>
       </c>
@@ -1176,7 +1188,7 @@
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="13" t="n">
         <v>6944000000</v>
       </c>
     </row>
@@ -1186,7 +1198,7 @@
           <t>Plus: cash &amp; ST investments</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="13" t="n">
         <v>457000000</v>
       </c>
     </row>
@@ -1196,7 +1208,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="17">
         <f>B29-B32+B33</f>
         <v/>
       </c>
@@ -1207,17 +1219,17 @@
           <t>Diluted shares outstanding</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
-        <v>125785461.675456</v>
+      <c r="B35" s="21" t="n">
+        <v>125785458.2698962</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Intrinsic per share</t>
         </is>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="22">
         <f>B34/B35</f>
         <v/>
       </c>
@@ -1228,17 +1240,17 @@
           <t>Current market price</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
-        <v>115.67</v>
+      <c r="B37" s="23" t="n">
+        <v>115.6</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="24">
         <f>(B36-B37)/B37</f>
         <v/>
       </c>
@@ -1258,158 +1270,158 @@
       <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="25" t="inlineStr">
         <is>
           <t>WACC ↓ / TermG →</t>
         </is>
       </c>
-      <c r="B42" s="25">
+      <c r="B42" s="26">
         <f>$B$12+-0.01</f>
         <v/>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="26">
         <f>$B$12+-0.005</f>
         <v/>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="26">
         <f>$B$12+0.0</f>
         <v/>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="26">
         <f>$B$12+0.005</f>
         <v/>
       </c>
-      <c r="F42" s="25">
+      <c r="F42" s="26">
         <f>$B$12+0.01</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="25">
+      <c r="A43" s="26">
         <f>$B$17+-0.01</f>
         <v/>
       </c>
-      <c r="B43" s="26">
+      <c r="B43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A43-B$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C43" s="26">
+      <c r="C43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A43-C$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A43-D$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A43-E$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F43" s="26">
+      <c r="F43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A43-F$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="25">
+      <c r="A44" s="26">
         <f>$B$17+-0.005</f>
         <v/>
       </c>
-      <c r="B44" s="26">
+      <c r="B44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A44-B$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C44" s="26">
+      <c r="C44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A44-C$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A44-D$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A44-E$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F44" s="26">
+      <c r="F44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A44-F$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="25">
+      <c r="A45" s="26">
         <f>$B$17+0.0</f>
         <v/>
       </c>
-      <c r="B45" s="26">
+      <c r="B45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A45-B$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C45" s="26">
+      <c r="C45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A45-C$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="28">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A45-D$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A45-E$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F45" s="26">
+      <c r="F45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A45-F$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="25">
+      <c r="A46" s="26">
         <f>$B$17+0.005</f>
         <v/>
       </c>
-      <c r="B46" s="26">
+      <c r="B46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A46-B$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C46" s="26">
+      <c r="C46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A46-C$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A46-D$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A46-E$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F46" s="26">
+      <c r="F46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A46-F$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="25">
+      <c r="A47" s="26">
         <f>$B$17+0.01</f>
         <v/>
       </c>
-      <c r="B47" s="26">
+      <c r="B47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A47-B$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C47" s="26">
+      <c r="C47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A47-C$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A47-D$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A47-E$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F47" s="26">
+      <c r="F47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A47-F$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
@@ -1465,59 +1477,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>P/E (TTM)</t>
         </is>
       </c>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>EV/Revenue</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>LDOS</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Leidos Holdings, Inc.</t>
         </is>
       </c>
-      <c r="C5" s="30" t="n">
-        <v>14549604352</v>
-      </c>
-      <c r="D5" s="31" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="E5" s="31" t="n">
-        <v>8.91</v>
-      </c>
-      <c r="F5" s="31" t="n">
-        <v>1.24</v>
+      <c r="C5" s="31" t="n">
+        <v>14540798976</v>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="F5" s="32" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="6">
@@ -1531,17 +1543,15 @@
           <t>Broadridge Financial Solutions,</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n">
-        <v>18590337024</v>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>17.190908</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>12.144</v>
-      </c>
-      <c r="F6" s="33" t="n">
-        <v>2.922</v>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="34" t="n">
+        <v>16.482868</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>11.866</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>2.855</v>
       </c>
     </row>
     <row r="7">
@@ -1555,17 +1565,15 @@
           <t>CDW Corporation</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n">
-        <v>18827024384</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>17.95006</v>
-      </c>
-      <c r="E7" s="33" t="n">
-        <v>12.092</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>1.046</v>
+      <c r="C7" s="33" t="n"/>
+      <c r="D7" s="34" t="n">
+        <v>18.02561</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>12.335</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>1.068</v>
       </c>
     </row>
     <row r="8">
@@ -1579,17 +1587,17 @@
           <t>Flex Ltd.</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n">
-        <v>37937807360</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>44.439915</v>
-      </c>
-      <c r="E8" s="33" t="n">
-        <v>21.155</v>
-      </c>
-      <c r="F8" s="33" t="n">
-        <v>1.561</v>
+      <c r="C8" s="33" t="n">
+        <v>41676812288</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>43.91892</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>21.545</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>1.559</v>
       </c>
     </row>
     <row r="9">
@@ -1603,17 +1611,17 @@
           <t>CGI Inc.</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
-        <v>15551533056</v>
-      </c>
-      <c r="D9" s="33" t="n">
-        <v>13.650736</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>6.383</v>
-      </c>
-      <c r="F9" s="33" t="n">
-        <v>1.142</v>
+      <c r="C9" s="33" t="n">
+        <v>15147566080</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>12.766144</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>6.439</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>1.143</v>
       </c>
     </row>
     <row r="10">
@@ -1627,17 +1635,15 @@
           <t>HP Inc.</t>
         </is>
       </c>
-      <c r="C10" s="32" t="n">
-        <v>26100477952</v>
-      </c>
-      <c r="D10" s="33" t="n">
-        <v>10.570371</v>
-      </c>
-      <c r="E10" s="33" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="F10" s="33" t="n">
-        <v>0.575</v>
+      <c r="C10" s="33" t="n"/>
+      <c r="D10" s="34" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>6.812</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1651,17 +1657,17 @@
           <t>Gartner, Inc.</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
-        <v>11084554240</v>
-      </c>
-      <c r="D11" s="33" t="n">
-        <v>16.375866</v>
-      </c>
-      <c r="E11" s="33" t="n">
-        <v>9.067</v>
-      </c>
-      <c r="F11" s="33" t="n">
-        <v>1.872</v>
+      <c r="C11" s="33" t="n">
+        <v>10111074304</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>14.922926</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>8.824999999999999</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>1.823</v>
       </c>
     </row>
     <row r="12">
@@ -1675,17 +1681,17 @@
           <t>NetApp, Inc.</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n">
-        <v>34181167104</v>
-      </c>
-      <c r="D12" s="33" t="n">
-        <v>27.474804</v>
-      </c>
-      <c r="E12" s="33" t="n">
-        <v>17.698</v>
-      </c>
-      <c r="F12" s="33" t="n">
-        <v>4.815</v>
+      <c r="C12" s="33" t="n">
+        <v>35027816448</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>28.110237</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>18.111</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>4.927</v>
       </c>
     </row>
     <row r="13">
@@ -1699,17 +1705,15 @@
           <t>Teledyne Technologies Incorpora</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n">
-        <v>29436606464</v>
-      </c>
-      <c r="D13" s="33" t="n">
-        <v>30.754114</v>
-      </c>
-      <c r="E13" s="33" t="n">
-        <v>19.972</v>
-      </c>
-      <c r="F13" s="33" t="n">
-        <v>4.989</v>
+      <c r="C13" s="33" t="n"/>
+      <c r="D13" s="34" t="n">
+        <v>31.746733</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>20.143</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>5.032</v>
       </c>
     </row>
     <row r="15">
@@ -1718,15 +1722,15 @@
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>MEDIAN(D6:D13)</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>MEDIAN(E6:E13)</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>MEDIAN(F6:F13)</f>
         <v/>
       </c>
@@ -1737,15 +1741,15 @@
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="35">
         <f>AVERAGE(D6:D13)</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="35">
         <f>AVERAGE(E6:E13)</f>
         <v/>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="35">
         <f>AVERAGE(F6:F13)</f>
         <v/>
       </c>
@@ -1756,13 +1760,13 @@
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="36" t="n">
         <v>0.167</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="36" t="n">
         <v>0.333</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="36" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -1594,10 +1594,10 @@
         <v>43.91892</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>21.545</v>
+        <v>21.248</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.559</v>
+        <v>1.541</v>
       </c>
     </row>
     <row r="9">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.836</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>285.37</v>
+        <v>293.68</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>115.6</v>
+        <v>128.025</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.469</v>
+        <v>1.294</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.844</v>
+        <v>0.829</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.667</v>
+        <v>0.611</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04620999813079834</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125785458.2698962</v>
+        <v>125785456.5280219</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>115.6</v>
+        <v>128.025</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>14540798976</v>
+        <v>16103683072</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>10.57</v>
+        <v>11.4</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.77</v>
+        <v>8.93</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="6">
@@ -1545,13 +1545,13 @@
       </c>
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="34" t="n">
-        <v>16.482868</v>
+        <v>17.003801</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>11.866</v>
+        <v>12.189</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.855</v>
+        <v>2.949</v>
       </c>
     </row>
     <row r="7">
@@ -1567,13 +1567,13 @@
       </c>
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="34" t="n">
-        <v>18.02561</v>
+        <v>17.235977</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>12.335</v>
+        <v>12.328</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>1.068</v>
+        <v>1.067</v>
       </c>
     </row>
     <row r="8">
@@ -1588,16 +1588,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>41676812288</v>
+        <v>46221545472</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>43.91892</v>
+        <v>48.310814</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>21.248</v>
+        <v>23.503</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.541</v>
+        <v>1.705</v>
       </c>
     </row>
     <row r="9">
@@ -1612,16 +1612,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>15147566080</v>
+        <v>15159990272</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>12.766144</v>
+        <v>12.754355</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>6.439</v>
+        <v>6.429</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.143</v>
+        <v>1.141</v>
       </c>
     </row>
     <row r="10">
@@ -1637,13 +1637,13 @@
       </c>
       <c r="C10" s="33" t="n"/>
       <c r="D10" s="34" t="n">
-        <v>10.1</v>
+        <v>10.7277775</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>6.812</v>
+        <v>7.113</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="11">
@@ -1658,16 +1658,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>10111074304</v>
+        <v>11736238080</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>14.922926</v>
+        <v>16.698114</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>8.824999999999999</v>
+        <v>8.851000000000001</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>1.823</v>
+        <v>1.828</v>
       </c>
     </row>
     <row r="12">
@@ -1682,16 +1682,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>35027816448</v>
+        <v>37335531520</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>28.110237</v>
+        <v>30.009462</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>18.111</v>
+        <v>19.355</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.927</v>
+        <v>5.266</v>
       </c>
     </row>
     <row r="13">
@@ -1707,13 +1707,13 @@
       </c>
       <c r="C13" s="33" t="n"/>
       <c r="D13" s="34" t="n">
-        <v>31.746733</v>
+        <v>32.57481</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>20.143</v>
+        <v>20.58</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.032</v>
+        <v>5.141</v>
       </c>
     </row>
     <row r="15">
@@ -1764,7 +1764,7 @@
         <v>0.167</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="36" t="n">
         <v>0.5</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.828</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>293.68</v>
+        <v>297.34</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>128.025</v>
+        <v>136.975</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.294</v>
+        <v>1.171</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.829</v>
+        <v>0.805</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.611</v>
+        <v>0.667</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04620999813079834</v>
+        <v>0.04654000282287598</v>
       </c>
     </row>
     <row r="6">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>6944000000</v>
+        <v>6577999872</v>
       </c>
     </row>
     <row r="33">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>457000000</v>
+        <v>748000000</v>
       </c>
     </row>
     <row r="34">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125785456.5280219</v>
+        <v>125492214.8421245</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>128.025</v>
+        <v>136.975</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>16103683072</v>
+        <v>17189296128</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>11.4</v>
+        <v>12.79</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>8.93</v>
+        <v>9.6</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="6">
@@ -1543,15 +1543,17 @@
           <t>Broadridge Financial Solutions,</t>
         </is>
       </c>
-      <c r="C6" s="33" t="n"/>
+      <c r="C6" s="33" t="n">
+        <v>19065585664</v>
+      </c>
       <c r="D6" s="34" t="n">
-        <v>17.003801</v>
+        <v>17.417707</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>12.189</v>
+        <v>12.107</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.949</v>
+        <v>2.929</v>
       </c>
     </row>
     <row r="7">
@@ -1565,15 +1567,17 @@
           <t>CDW Corporation</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n"/>
+      <c r="C7" s="33" t="n">
+        <v>17098007552</v>
+      </c>
       <c r="D7" s="34" t="n">
-        <v>17.235977</v>
+        <v>16.4381</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>12.328</v>
+        <v>11.844</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>1.067</v>
+        <v>1.013</v>
       </c>
     </row>
     <row r="8">
@@ -1588,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>46221545472</v>
+        <v>45100408832</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>48.310814</v>
+        <v>47.138996</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>23.503</v>
+        <v>22.797</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.705</v>
+        <v>1.654</v>
       </c>
     </row>
     <row r="9">
@@ -1612,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>15159990272</v>
+        <v>15418834944</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>12.754355</v>
+        <v>12.994764</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>6.429</v>
+        <v>6.511</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.141</v>
+        <v>1.155</v>
       </c>
     </row>
     <row r="10">
@@ -1637,13 +1641,13 @@
       </c>
       <c r="C10" s="33" t="n"/>
       <c r="D10" s="34" t="n">
-        <v>10.7277775</v>
+        <v>11.035185</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>7.113</v>
+        <v>6.989</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.584</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="11">
@@ -1658,16 +1662,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>11736238080</v>
+        <v>11851167744</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>16.698114</v>
+        <v>16.861635</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>8.851000000000001</v>
+        <v>9.763999999999999</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>1.828</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="12">
@@ -1682,16 +1686,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>37335531520</v>
+        <v>37369872384</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>30.009462</v>
+        <v>29.94261</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>19.355</v>
+        <v>19.461</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.266</v>
+        <v>5.294</v>
       </c>
     </row>
     <row r="13">
@@ -1705,15 +1709,17 @@
           <t>Teledyne Technologies Incorpora</t>
         </is>
       </c>
-      <c r="C13" s="33" t="n"/>
+      <c r="C13" s="33" t="n">
+        <v>32000944128</v>
+      </c>
       <c r="D13" s="34" t="n">
-        <v>32.57481</v>
+        <v>33.365635</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>20.58</v>
+        <v>21.073</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.141</v>
+        <v>5.264</v>
       </c>
     </row>
     <row r="15">
@@ -1764,7 +1770,7 @@
         <v>0.167</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="F17" s="36" t="n">
         <v>0.5</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.828</v>
+        <v>0.803</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>297.34</v>
+        <v>291.99</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>136.975</v>
+        <v>141.605</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.171</v>
+        <v>1.062</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.805</v>
+        <v>0.793</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.667</v>
+        <v>0.611</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04654000282287598</v>
+        <v>0.04734000205993652</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125492214.8421245</v>
+        <v>125492206.9700929</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>136.975</v>
+        <v>141.605</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>17189296128</v>
+        <v>17770323968</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.79</v>
+        <v>13.21</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.6</v>
+        <v>9.92</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>19065585664</v>
+        <v>20563832832</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>17.417707</v>
+        <v>18.786459</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>12.107</v>
+        <v>12.974</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.929</v>
+        <v>3.139</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>17098007552</v>
+        <v>17387423744</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>16.4381</v>
+        <v>16.716347</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.844</v>
+        <v>11.32</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>1.013</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>45100408832</v>
+        <v>40730374144</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>47.138996</v>
+        <v>42.57143</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>22.797</v>
+        <v>20.651</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.654</v>
+        <v>1.498</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>15418834944</v>
+        <v>15470603264</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>12.994764</v>
+        <v>12.903281</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>6.511</v>
+        <v>6.517</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.155</v>
+        <v>1.157</v>
       </c>
     </row>
     <row r="10">
@@ -1641,13 +1641,13 @@
       </c>
       <c r="C10" s="33" t="n"/>
       <c r="D10" s="34" t="n">
-        <v>11.035185</v>
+        <v>11.064815</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>6.989</v>
+        <v>7.239</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.574</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="11">
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>11851167744</v>
+        <v>12332362752</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>16.861635</v>
+        <v>17.56205</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>9.763999999999999</v>
+        <v>10.168</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>2.09</v>
+        <v>2.177</v>
       </c>
     </row>
     <row r="12">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>37369872384</v>
+        <v>37992919040</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>29.94261</v>
+        <v>30.537855</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>19.461</v>
+        <v>19.599</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.294</v>
+        <v>5.332</v>
       </c>
     </row>
     <row r="13">
@@ -1710,16 +1710,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>32000944128</v>
+        <v>29224470528</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>33.365635</v>
+        <v>30.500242</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>21.073</v>
+        <v>19.514</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.264</v>
+        <v>4.875</v>
       </c>
     </row>
     <row r="15">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0.333</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-22 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>291.99</v>
+        <v>291.73</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>141.605</v>
+        <v>141.39</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.062</v>
+        <v>1.063</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.793</v>
+        <v>0.794</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04734000205993652</v>
+        <v>0.0473799991607666</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125492206.9700929</v>
+        <v>125492210.3119033</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>141.605</v>
+        <v>141.39</v>
       </c>
     </row>
     <row r="38">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>17770323968</v>
+        <v>17743343616</v>
       </c>
       <c r="D5" s="32" t="n">
         <v>13.21</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>20563832832</v>
+        <v>20772491264</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>18.786459</v>
+        <v>18.977081</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>12.974</v>
+        <v>13.206</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.139</v>
+        <v>3.195</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>17387423744</v>
+        <v>17158641664</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>16.716347</v>
+        <v>16.496395</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.32</v>
+        <v>11.55</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.969</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>40730374144</v>
+        <v>40800559104</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>42.57143</v>
+        <v>42.48077</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>20.651</v>
+        <v>20.674</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.498</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>15470603264</v>
+        <v>15526514688</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>12.903281</v>
+        <v>12.861064</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>6.517</v>
+        <v>6.567</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.157</v>
+        <v>1.166</v>
       </c>
     </row>
     <row r="10">
@@ -1641,13 +1641,13 @@
       </c>
       <c r="C10" s="33" t="n"/>
       <c r="D10" s="34" t="n">
-        <v>11.064815</v>
+        <v>11.003703</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>7.239</v>
+        <v>7.286</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.594</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="11">
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>12332362752</v>
+        <v>12370883584</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>17.56205</v>
+        <v>17.601078</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>10.168</v>
+        <v>10.269</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>2.177</v>
+        <v>2.199</v>
       </c>
     </row>
     <row r="12">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>37992919040</v>
+        <v>37729964032</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>30.537855</v>
+        <v>30.326498</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>19.599</v>
+        <v>19.543</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.332</v>
+        <v>5.317</v>
       </c>
     </row>
     <row r="13">
@@ -1710,16 +1710,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>29224470528</v>
+        <v>29489162240</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>30.500242</v>
+        <v>30.77649</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.514</v>
+        <v>19.578</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>4.875</v>
+        <v>4.891</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-22 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
         <v>40800559104</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>42.48077</v>
+        <v>42.810078</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>20.674</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.803</v>
+        <v>0.829</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>291.73</v>
+        <v>298.09</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>141.39</v>
+        <v>135.43</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.063</v>
+        <v>1.201</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.794</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.611</v>
+        <v>0.667</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0473799991607666</v>
+        <v>0.0464300012588501</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125492210.3119033</v>
+        <v>125492201.8459721</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>141.39</v>
+        <v>135.43</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>17743343616</v>
+        <v>16995408896</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.21</v>
+        <v>12.65</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.92</v>
+        <v>9.76</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>20772491264</v>
+        <v>21062014976</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>18.977081</v>
+        <v>19.221561</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>13.206</v>
+        <v>13.412</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.195</v>
+        <v>3.245</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>17158641664</v>
+        <v>17518692352</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>16.496395</v>
+        <v>16.256382</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.55</v>
+        <v>11.256</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.988</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>40800559104</v>
+        <v>39808712704</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>42.810078</v>
+        <v>41.60811</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>20.674</v>
+        <v>20.013</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.5</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>15526514688</v>
+        <v>15358782464</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>12.861064</v>
+        <v>12.700342</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>6.567</v>
+        <v>6.556</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.166</v>
+        <v>1.164</v>
       </c>
     </row>
     <row r="10">
@@ -1641,13 +1641,13 @@
       </c>
       <c r="C10" s="33" t="n"/>
       <c r="D10" s="34" t="n">
-        <v>11.003703</v>
+        <v>10.842592</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>7.286</v>
+        <v>7.067</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.598</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="11">
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>12370883584</v>
+        <v>12680945664</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>17.601078</v>
+        <v>18.074707</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>10.269</v>
+        <v>10.583</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>2.199</v>
+        <v>2.266</v>
       </c>
     </row>
     <row r="12">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>37729964032</v>
+        <v>36627124224</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>30.326498</v>
+        <v>29.3937</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>19.543</v>
+        <v>18.98</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.317</v>
+        <v>5.164</v>
       </c>
     </row>
     <row r="13">
@@ -1710,16 +1710,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>29489162240</v>
+        <v>29042366464</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>30.77649</v>
+        <v>30.280888</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.578</v>
+        <v>19.26</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>4.891</v>
+        <v>4.811</v>
       </c>
     </row>
     <row r="15">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0.333</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.829</v>
+        <v>0.83</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>298.09</v>
+        <v>288.73</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>135.43</v>
+        <v>133.05</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.201</v>
+        <v>1.17</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.0464300012588501</v>
+        <v>0.04783999919891357</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125492201.8459721</v>
+        <v>125492212.0706501</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>135.43</v>
+        <v>133.05</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>16995408896</v>
+        <v>16696738816</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.65</v>
+        <v>12.42</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.76</v>
+        <v>9.48</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>21062014976</v>
+        <v>19712090112</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>19.221561</v>
+        <v>18.62931</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>13.412</v>
+        <v>12.62</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.245</v>
+        <v>3.053</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>17518692352</v>
+        <v>19050156032</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>16.256382</v>
+        <v>18.314905</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.256</v>
+        <v>12.491</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.963</v>
+        <v>1.069</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>39808712704</v>
+        <v>40453320704</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>41.60811</v>
+        <v>42.44574</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>20.013</v>
+        <v>20.51</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.452</v>
+        <v>1.488</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>15358782464</v>
+        <v>15251103744</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>12.700342</v>
+        <v>12.67642</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>6.556</v>
+        <v>6.474</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.164</v>
+        <v>1.149</v>
       </c>
     </row>
     <row r="10">
@@ -1639,15 +1639,17 @@
           <t>HP Inc.</t>
         </is>
       </c>
-      <c r="C10" s="33" t="n"/>
+      <c r="C10" s="33" t="n">
+        <v>29434456064</v>
+      </c>
       <c r="D10" s="34" t="n">
-        <v>10.842592</v>
+        <v>12.179104</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>7.067</v>
+        <v>7.542</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.58</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="11">
@@ -1662,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>12680945664</v>
+        <v>11772231680</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>18.074707</v>
+        <v>16.749327</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>10.583</v>
+        <v>9.837</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>2.266</v>
+        <v>2.106</v>
       </c>
     </row>
     <row r="12">
@@ -1686,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>36627124224</v>
+        <v>36453404672</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>29.3937</v>
+        <v>26.250353</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>18.98</v>
+        <v>16.903</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>5.164</v>
+        <v>4.791</v>
       </c>
     </row>
     <row r="13">
@@ -1710,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>29042366464</v>
+        <v>28307091456</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>30.280888</v>
+        <v>29.585758</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.26</v>
+        <v>18.755</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>4.811</v>
+        <v>4.685</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-06 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.83</v>
+        <v>0.852</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.667</v>
+        <v>0.722</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>19712090112</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>18.62931</v>
+        <v>18.027111</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>12.62</v>
@@ -1643,13 +1643,13 @@
         <v>29434456064</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.179104</v>
+        <v>12.458015</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>7.542</v>
+        <v>7.68</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.591</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="11">
@@ -1718,10 +1718,10 @@
         <v>29.585758</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>18.755</v>
+        <v>18.836</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>4.685</v>
+        <v>4.705</v>
       </c>
     </row>
     <row r="15">
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0.333</v>

--- a/app/reports/LDOS_research.xlsx
+++ b/app/reports/LDOS_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-06 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.852</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>288.73</v>
+        <v>285.47</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>133.05</v>
+        <v>129.175</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.722</v>
+        <v>0.611</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04783999919891357</v>
+        <v>0.04835000038146973</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>125492212.0706501</v>
+        <v>125492212.7036965</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>133.05</v>
+        <v>129.175</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>16696738816</v>
+        <v>16210456576</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.42</v>
+        <v>12.06</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.48</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>19712090112</v>
+        <v>19155662848</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>18.027111</v>
+        <v>17.518248</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>12.62</v>
+        <v>12.351</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>3.053</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>19050156032</v>
+        <v>17672462336</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>18.314905</v>
+        <v>16.990385</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>12.491</v>
+        <v>12</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>1.069</v>
+        <v>1.027</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>40453320704</v>
+        <v>41746231296</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>42.44574</v>
+        <v>43.633205</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>20.51</v>
+        <v>21.345</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.488</v>
+        <v>1.548</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>15251103744</v>
+        <v>14195019776</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>12.67642</v>
+        <v>11.778351</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>6.474</v>
+        <v>6.264</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>1.149</v>
+        <v>1.112</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>29434456064</v>
+        <v>28604809216</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.458015</v>
+        <v>12.106871</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>7.68</v>
+        <v>7.394</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.602</v>
+        <v>0.579</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>11772231680</v>
+        <v>10750482432</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>16.749327</v>
+        <v>15.323133</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>9.837</v>
+        <v>9.206</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>2.106</v>
+        <v>1.971</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>36453404672</v>
+        <v>36526080000</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>26.250353</v>
+        <v>26.302689</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>16.903</v>
+        <v>17.235</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>4.791</v>
+        <v>4.885</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>28307091456</v>
+        <v>27640033280</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>29.585758</v>
+        <v>28.818752</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>18.836</v>
+        <v>18.674</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>4.705</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="15">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="36" t="n">
         <v>0.5</v>
